--- a/www/terminologies/ASS-X13-AgregatClientele.xlsx
+++ b/www/terminologies/ASS-X13-AgregatClientele.xlsx
@@ -99,13 +99,13 @@
     <t>Target</t>
   </si>
   <si>
-    <t>https://mos.esante.gouv.fr/NOS/TRE_R293-AgregatClienteleNiv2/FHIR/TRE-R293-AgregatClienteleNiv2|20231215120000</t>
+    <t>https://mos.esante.gouv.fr/NOS/TRE_R293-AgregatClienteleNiv2/FHIR/TRE-R293-AgregatClienteleNiv2</t>
   </si>
   <si>
     <t/>
   </si>
   <si>
-    <t>https://mos.esante.gouv.fr/NOS/TRE_R294-AgregatClienteleNiv3/FHIR/TRE-R294-AgregatClienteleNiv3|20231215120000</t>
+    <t>https://mos.esante.gouv.fr/NOS/TRE_R294-AgregatClienteleNiv3/FHIR/TRE-R294-AgregatClienteleNiv3</t>
   </si>
   <si>
     <t>1000</t>

--- a/www/terminologies/ASS-X13-AgregatClientele.xlsx
+++ b/www/terminologies/ASS-X13-AgregatClientele.xlsx
@@ -13,7 +13,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="416" uniqueCount="61">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="428" uniqueCount="61">
   <si>
     <t>Property</t>
   </si>
@@ -36,7 +36,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>20240628120000</t>
+    <t>20260629120000</t>
   </si>
   <si>
     <t>Name</t>
@@ -63,7 +63,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-06-28T12:00:00+01:00</t>
+    <t>2026-06-29T12:00:00+01:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -449,7 +449,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:E129"/>
+  <dimension ref="A1:E133"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <sheetData>
     <row r="1">
@@ -1834,7 +1834,7 @@
         <v>32</v>
       </c>
       <c r="D106" t="s" s="2">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="E106" s="2"/>
     </row>
@@ -1847,7 +1847,7 @@
         <v>32</v>
       </c>
       <c r="D107" t="s" s="2">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="E107" s="2"/>
     </row>
@@ -1860,7 +1860,7 @@
         <v>32</v>
       </c>
       <c r="D108" t="s" s="2">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="E108" s="2"/>
     </row>
@@ -1873,72 +1873,72 @@
         <v>32</v>
       </c>
       <c r="D109" t="s" s="2">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="E109" s="2"/>
     </row>
     <row r="110">
       <c r="A110" t="s" s="2">
-        <v>54</v>
+        <v>51</v>
       </c>
       <c r="B110" s="2"/>
       <c r="C110" t="s" s="2">
         <v>32</v>
       </c>
       <c r="D110" t="s" s="2">
-        <v>55</v>
+        <v>53</v>
       </c>
       <c r="E110" s="2"/>
     </row>
     <row r="111">
       <c r="A111" t="s" s="2">
-        <v>56</v>
+        <v>51</v>
       </c>
       <c r="B111" s="2"/>
       <c r="C111" t="s" s="2">
         <v>32</v>
       </c>
       <c r="D111" t="s" s="2">
-        <v>57</v>
+        <v>53</v>
       </c>
       <c r="E111" s="2"/>
     </row>
     <row r="112">
       <c r="A112" t="s" s="2">
-        <v>56</v>
+        <v>51</v>
       </c>
       <c r="B112" s="2"/>
       <c r="C112" t="s" s="2">
         <v>32</v>
       </c>
       <c r="D112" t="s" s="2">
-        <v>57</v>
+        <v>53</v>
       </c>
       <c r="E112" s="2"/>
     </row>
     <row r="113">
       <c r="A113" t="s" s="2">
-        <v>56</v>
+        <v>51</v>
       </c>
       <c r="B113" s="2"/>
       <c r="C113" t="s" s="2">
         <v>32</v>
       </c>
       <c r="D113" t="s" s="2">
-        <v>57</v>
+        <v>53</v>
       </c>
       <c r="E113" s="2"/>
     </row>
     <row r="114">
       <c r="A114" t="s" s="2">
-        <v>56</v>
+        <v>54</v>
       </c>
       <c r="B114" s="2"/>
       <c r="C114" t="s" s="2">
         <v>32</v>
       </c>
       <c r="D114" t="s" s="2">
-        <v>58</v>
+        <v>55</v>
       </c>
       <c r="E114" s="2"/>
     </row>
@@ -1951,7 +1951,7 @@
         <v>32</v>
       </c>
       <c r="D115" t="s" s="2">
-        <v>59</v>
+        <v>57</v>
       </c>
       <c r="E115" s="2"/>
     </row>
@@ -1964,7 +1964,7 @@
         <v>32</v>
       </c>
       <c r="D116" t="s" s="2">
-        <v>59</v>
+        <v>57</v>
       </c>
       <c r="E116" s="2"/>
     </row>
@@ -1977,7 +1977,7 @@
         <v>32</v>
       </c>
       <c r="D117" t="s" s="2">
-        <v>59</v>
+        <v>57</v>
       </c>
       <c r="E117" s="2"/>
     </row>
@@ -1990,7 +1990,7 @@
         <v>32</v>
       </c>
       <c r="D118" t="s" s="2">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="E118" s="2"/>
     </row>
@@ -2068,7 +2068,7 @@
         <v>32</v>
       </c>
       <c r="D124" t="s" s="2">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="E124" s="2"/>
     </row>
@@ -2081,7 +2081,7 @@
         <v>32</v>
       </c>
       <c r="D125" t="s" s="2">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="E125" s="2"/>
     </row>
@@ -2094,7 +2094,7 @@
         <v>32</v>
       </c>
       <c r="D126" t="s" s="2">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="E126" s="2"/>
     </row>
@@ -2107,7 +2107,7 @@
         <v>32</v>
       </c>
       <c r="D127" t="s" s="2">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="E127" s="2"/>
     </row>
@@ -2136,6 +2136,58 @@
         <v>60</v>
       </c>
       <c r="E129" s="2"/>
+    </row>
+    <row r="130">
+      <c r="A130" t="s" s="2">
+        <v>56</v>
+      </c>
+      <c r="B130" s="2"/>
+      <c r="C130" t="s" s="2">
+        <v>32</v>
+      </c>
+      <c r="D130" t="s" s="2">
+        <v>60</v>
+      </c>
+      <c r="E130" s="2"/>
+    </row>
+    <row r="131">
+      <c r="A131" t="s" s="2">
+        <v>56</v>
+      </c>
+      <c r="B131" s="2"/>
+      <c r="C131" t="s" s="2">
+        <v>32</v>
+      </c>
+      <c r="D131" t="s" s="2">
+        <v>60</v>
+      </c>
+      <c r="E131" s="2"/>
+    </row>
+    <row r="132">
+      <c r="A132" t="s" s="2">
+        <v>56</v>
+      </c>
+      <c r="B132" s="2"/>
+      <c r="C132" t="s" s="2">
+        <v>32</v>
+      </c>
+      <c r="D132" t="s" s="2">
+        <v>60</v>
+      </c>
+      <c r="E132" s="2"/>
+    </row>
+    <row r="133">
+      <c r="A133" t="s" s="2">
+        <v>56</v>
+      </c>
+      <c r="B133" s="2"/>
+      <c r="C133" t="s" s="2">
+        <v>32</v>
+      </c>
+      <c r="D133" t="s" s="2">
+        <v>60</v>
+      </c>
+      <c r="E133" s="2"/>
     </row>
   </sheetData>
   <pageMargins bottom="0.75" footer="0.3" header="0.3" left="0.7" right="0.7" top="0.75"/>

--- a/www/terminologies/ASS-X13-AgregatClientele.xlsx
+++ b/www/terminologies/ASS-X13-AgregatClientele.xlsx
@@ -13,7 +13,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="428" uniqueCount="61">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="416" uniqueCount="61">
   <si>
     <t>Property</t>
   </si>
@@ -36,7 +36,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>20260629120000</t>
+    <t>20240628120000</t>
   </si>
   <si>
     <t>Name</t>
@@ -63,7 +63,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-06-29T12:00:00+01:00</t>
+    <t>2024-06-28T12:00:00+01:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -449,7 +449,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:E133"/>
+  <dimension ref="A1:E129"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <sheetData>
     <row r="1">
@@ -1834,7 +1834,7 @@
         <v>32</v>
       </c>
       <c r="D106" t="s" s="2">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="E106" s="2"/>
     </row>
@@ -1847,7 +1847,7 @@
         <v>32</v>
       </c>
       <c r="D107" t="s" s="2">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="E107" s="2"/>
     </row>
@@ -1860,7 +1860,7 @@
         <v>32</v>
       </c>
       <c r="D108" t="s" s="2">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="E108" s="2"/>
     </row>
@@ -1873,72 +1873,72 @@
         <v>32</v>
       </c>
       <c r="D109" t="s" s="2">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="E109" s="2"/>
     </row>
     <row r="110">
       <c r="A110" t="s" s="2">
-        <v>51</v>
+        <v>54</v>
       </c>
       <c r="B110" s="2"/>
       <c r="C110" t="s" s="2">
         <v>32</v>
       </c>
       <c r="D110" t="s" s="2">
-        <v>53</v>
+        <v>55</v>
       </c>
       <c r="E110" s="2"/>
     </row>
     <row r="111">
       <c r="A111" t="s" s="2">
-        <v>51</v>
+        <v>56</v>
       </c>
       <c r="B111" s="2"/>
       <c r="C111" t="s" s="2">
         <v>32</v>
       </c>
       <c r="D111" t="s" s="2">
-        <v>53</v>
+        <v>57</v>
       </c>
       <c r="E111" s="2"/>
     </row>
     <row r="112">
       <c r="A112" t="s" s="2">
-        <v>51</v>
+        <v>56</v>
       </c>
       <c r="B112" s="2"/>
       <c r="C112" t="s" s="2">
         <v>32</v>
       </c>
       <c r="D112" t="s" s="2">
-        <v>53</v>
+        <v>57</v>
       </c>
       <c r="E112" s="2"/>
     </row>
     <row r="113">
       <c r="A113" t="s" s="2">
-        <v>51</v>
+        <v>56</v>
       </c>
       <c r="B113" s="2"/>
       <c r="C113" t="s" s="2">
         <v>32</v>
       </c>
       <c r="D113" t="s" s="2">
-        <v>53</v>
+        <v>57</v>
       </c>
       <c r="E113" s="2"/>
     </row>
     <row r="114">
       <c r="A114" t="s" s="2">
-        <v>54</v>
+        <v>56</v>
       </c>
       <c r="B114" s="2"/>
       <c r="C114" t="s" s="2">
         <v>32</v>
       </c>
       <c r="D114" t="s" s="2">
-        <v>55</v>
+        <v>58</v>
       </c>
       <c r="E114" s="2"/>
     </row>
@@ -1951,7 +1951,7 @@
         <v>32</v>
       </c>
       <c r="D115" t="s" s="2">
-        <v>57</v>
+        <v>59</v>
       </c>
       <c r="E115" s="2"/>
     </row>
@@ -1964,7 +1964,7 @@
         <v>32</v>
       </c>
       <c r="D116" t="s" s="2">
-        <v>57</v>
+        <v>59</v>
       </c>
       <c r="E116" s="2"/>
     </row>
@@ -1977,7 +1977,7 @@
         <v>32</v>
       </c>
       <c r="D117" t="s" s="2">
-        <v>57</v>
+        <v>59</v>
       </c>
       <c r="E117" s="2"/>
     </row>
@@ -1990,7 +1990,7 @@
         <v>32</v>
       </c>
       <c r="D118" t="s" s="2">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="E118" s="2"/>
     </row>
@@ -2068,7 +2068,7 @@
         <v>32</v>
       </c>
       <c r="D124" t="s" s="2">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="E124" s="2"/>
     </row>
@@ -2081,7 +2081,7 @@
         <v>32</v>
       </c>
       <c r="D125" t="s" s="2">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="E125" s="2"/>
     </row>
@@ -2094,7 +2094,7 @@
         <v>32</v>
       </c>
       <c r="D126" t="s" s="2">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="E126" s="2"/>
     </row>
@@ -2107,7 +2107,7 @@
         <v>32</v>
       </c>
       <c r="D127" t="s" s="2">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="E127" s="2"/>
     </row>
@@ -2136,58 +2136,6 @@
         <v>60</v>
       </c>
       <c r="E129" s="2"/>
-    </row>
-    <row r="130">
-      <c r="A130" t="s" s="2">
-        <v>56</v>
-      </c>
-      <c r="B130" s="2"/>
-      <c r="C130" t="s" s="2">
-        <v>32</v>
-      </c>
-      <c r="D130" t="s" s="2">
-        <v>60</v>
-      </c>
-      <c r="E130" s="2"/>
-    </row>
-    <row r="131">
-      <c r="A131" t="s" s="2">
-        <v>56</v>
-      </c>
-      <c r="B131" s="2"/>
-      <c r="C131" t="s" s="2">
-        <v>32</v>
-      </c>
-      <c r="D131" t="s" s="2">
-        <v>60</v>
-      </c>
-      <c r="E131" s="2"/>
-    </row>
-    <row r="132">
-      <c r="A132" t="s" s="2">
-        <v>56</v>
-      </c>
-      <c r="B132" s="2"/>
-      <c r="C132" t="s" s="2">
-        <v>32</v>
-      </c>
-      <c r="D132" t="s" s="2">
-        <v>60</v>
-      </c>
-      <c r="E132" s="2"/>
-    </row>
-    <row r="133">
-      <c r="A133" t="s" s="2">
-        <v>56</v>
-      </c>
-      <c r="B133" s="2"/>
-      <c r="C133" t="s" s="2">
-        <v>32</v>
-      </c>
-      <c r="D133" t="s" s="2">
-        <v>60</v>
-      </c>
-      <c r="E133" s="2"/>
     </row>
   </sheetData>
   <pageMargins bottom="0.75" footer="0.3" header="0.3" left="0.7" right="0.7" top="0.75"/>
